--- a/InputData/indst/_cement/SCMEI/SCM Production Energy per Ton of Substitution.xlsx
+++ b/InputData/indst/_cement/SCMEI/SCM Production Energy per Ton of Substitution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\indst\_cement\SCMEI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BD48FE7-93DA-4CBA-9882-DBDEE2D7EABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86C3C6B2-DA92-4760-BD78-211BE8226419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>SCMEI SCM Production Energy per Ton of Substitution</t>
   </si>
@@ -44,36 +44,9 @@
     <t>Sources:</t>
   </si>
   <si>
-    <t>Technology Roadmap: Low-Carbon Transition in the Cement Industry</t>
-  </si>
-  <si>
-    <t>https://www.iea.org/reports/technology-roadmap-low-carbon-transition-in-the-cement-industry</t>
-  </si>
-  <si>
-    <t>LC3 - Low Carbon Cements based on Limestone Calcined Clay</t>
-  </si>
-  <si>
-    <t>https://lc3.ch/</t>
-  </si>
-  <si>
     <t>Notes:</t>
   </si>
   <si>
-    <t>SCMEI derivation: blended calcined-clay + byproduct-SCM production energy</t>
-  </si>
-  <si>
-    <t>Calcined-clay calcination energy (BTU/metric ton clay, ~2 GJ/t per LC3 literature)</t>
-  </si>
-  <si>
-    <t>Byproduct-SCM share of SCM blend (fly ash, slag, natural pozzolans - ~0 additional process energy)</t>
-  </si>
-  <si>
-    <t>Byproduct-SCM production energy (BTU/metric ton, waste/byproduct stream)</t>
-  </si>
-  <si>
-    <t>SCMEI = clay share x clay energy + byproduct share x byproduct energy</t>
-  </si>
-  <si>
     <t>Value</t>
   </si>
   <si>
@@ -89,63 +62,132 @@
     <t>Energy to calcine clay</t>
   </si>
   <si>
-    <t>LC3 Project (EPFL and partners)</t>
-  </si>
-  <si>
-    <t>Calcined clay for LC3-type cement is made by flash-calcining kaolinitic clay at roughly 700-850 C, reported at about 2 GJ per metric ton of calcined clay, well below the 3.5-4 GJ per ton needed to make clinker. We use 2,000,000 BTU per metric ton (about 2.1 GJ), entered on the 'Derivation' tab. The figure comes from the project website and summary literature, not a single audited life-cycle study.</t>
-  </si>
-  <si>
-    <t>Cross-check that calcined clay carries a real energy cost</t>
-  </si>
-  <si>
-    <t>International Energy Agency</t>
-  </si>
-  <si>
-    <t>The roadmap reports that moving to calcined-clay blends such as LC3 raises plant thermal energy use by roughly 11% relative to plain Portland cement because of the added calcination step. We use it only to confirm that calcined clay has a real energy cost, unlike byproduct materials; it is not a per-ton figure and does not enter the calculation.</t>
-  </si>
-  <si>
     <t>Purpose and layout</t>
   </si>
   <si>
+    <t>How the value is built</t>
+  </si>
+  <si>
+    <t>Fuel</t>
+  </si>
+  <si>
+    <t>Unit: BTU/metric ton SCM</t>
+  </si>
+  <si>
+    <t>SCMEI: thermal energy to produce the marginal SCM mix (share-weighted)</t>
+  </si>
+  <si>
+    <t>SCM type</t>
+  </si>
+  <si>
+    <t>Share of marginal SCM</t>
+  </si>
+  <si>
+    <t>Thermal energy (GJ/metric ton)</t>
+  </si>
+  <si>
+    <t>Calcined clay (flash or rotary calcination)</t>
+  </si>
+  <si>
+    <t>Additional limestone</t>
+  </si>
+  <si>
+    <t>Fly ash (75% harvested and dried at 0.9 GJ/t; 25% fresh at 0)</t>
+  </si>
+  <si>
+    <t>Granulated blast-furnace slag (drying)</t>
+  </si>
+  <si>
+    <t>Natural pozzolan (drying)</t>
+  </si>
+  <si>
+    <t>Total / weighted energy (GJ/t)</t>
+  </si>
+  <si>
+    <t>BTU per GJ</t>
+  </si>
+  <si>
+    <t>RILEM TC 282-CCL (Hanein et al.), Materials and Structures</t>
+  </si>
+  <si>
+    <t>Clay calcination technology: state-of-the-art review by the RILEM TC 282-CCL</t>
+  </si>
+  <si>
+    <t>https://eprints.whiterose.ac.uk/id/eprint/181859/</t>
+  </si>
+  <si>
+    <t>The theoretical minimum is 1.51 MJ per kg of calcined clay; at the 50-70% thermal efficiency of real calciners that is 2.2-3.0 GJ per metric ton. LC3 project material (Grimmeissen, 2019) gives 2.0-2.5 GJ for flash calciners and 2.8-3.0 GJ for rotary kilns. We use 2.3 GJ.</t>
+  </si>
+  <si>
+    <t>Limits on slag supply</t>
+  </si>
+  <si>
+    <t>U.S. Geological Survey</t>
+  </si>
+  <si>
+    <t>Mineral Commodity Summaries 2026: Iron and Steel Slag</t>
+  </si>
+  <si>
+    <t>https://pubs.usgs.gov/periodicals/mcs2026/mcs2026-iron-steel-slag.pdf</t>
+  </si>
+  <si>
+    <t>Granulated blast-furnace slag is under 30% of the 16 million metric tons of slag sold in the U.S., and imports of about 2.1 million tons (mostly from Japan) are expected to decline, so slag cannot supply much of the increase.</t>
+  </si>
+  <si>
+    <t>Which SCM grows</t>
+  </si>
+  <si>
+    <t>U.S. Department of Energy</t>
+  </si>
+  <si>
+    <t>Transformative Pathways for U.S. Industry: Unlocking American Innovation</t>
+  </si>
+  <si>
+    <t>https://www.energy.gov/sites/default/files/2025-01/transformative-pathways-for-us-industry.pdf</t>
+  </si>
+  <si>
+    <t>Assumes all growth in SCM use comes from limestone calcined clay (LC3), which sets the upper bound on the calcined-clay share. Fresh coal fly ash is declining with coal plant retirements (ACAA reports 14.6 million tons used in 2024), leaving harvested landfill and pond ash as the growing source.</t>
+  </si>
+  <si>
+    <t>Processing energy for natural pozzolans</t>
+  </si>
+  <si>
+    <t>Geofortis Pozzolans (environmental product declaration, ASTM program)</t>
+  </si>
+  <si>
+    <t>Environmental Product Declaration: natural pozzolan</t>
+  </si>
+  <si>
+    <t>https://www.astm.org/v3/assets/blt5eb0a2cb04534832/bltbb4ced4c2501671d/697b20f91ff8dac01e1f2afc/944.Geofortis_EPD_Revised.pdf</t>
+  </si>
+  <si>
+    <t>Natural pozzolan is gas-dried and ball-milled; we infer about 0.3 GJ of heat per metric ton. Some producers use quarry fines that need almost no heat.</t>
+  </si>
+  <si>
     <t>This file gives the thermal energy needed to produce one metric ton of the supplementary cementitious material (SCM) that replaces clinker when the clinker-substitution lever is used, in BTU per metric ton. The EPS cement module multiplies it by the extra SCM tonnage the lever creates and adds the result to the cement industry's natural gas use. It is a single number, not a time series.
-The tabs run from inputs to output. 'Derivation' holds the blend assumptions and the arithmetic, and these are the values a user might change. 'Checks' tests that the result is between 0 and 3,000,000 BTU per ton. The 'SCMEI' tab reads from 'Derivation' by formula and is what gets exported to SCMEI.csv.</t>
-  </si>
-  <si>
-    <t>How the value is built</t>
-  </si>
-  <si>
-    <t>We treat the SCM as a half-and-half blend. Calcined clay needs about 2,000,000 BTU per ton to calcine. Byproduct SCMs such as fly ash, slag, and natural pozzolans are waste or byproduct streams from other industries and need essentially no added process energy, so we set them to zero. The blend is 50% x 2,000,000 + 50% x 0 = 1,000,000 BTU per metric ton. The 50% clay share is our own judgment; no U.S. forecast of the SCM mix was used, and it should move if the clay share of SCM supply is better known.</t>
-  </si>
-  <si>
-    <t>Fuel</t>
-  </si>
-  <si>
-    <t>All of the energy is booked to natural gas, because clay calciners and kilns of this type are conventionally gas- or coal-fired. The byproduct share contributes no fuel, so no other fuel split is needed.</t>
-  </si>
-  <si>
-    <t>Calcined-clay share of SCM blend (EI judgment)</t>
-  </si>
-  <si>
-    <t>Unit: BTU/metric ton SCM</t>
+'Derivation' holds the mix of SCM types and the energy each needs, and these are the values a user might change. 'Checks' tests that the result is between 0 and 3,000,000 BTU per ton. The 'SCMEI' tab reads from 'Derivation' by formula and is exported to SCMEI.csv.</t>
+  </si>
+  <si>
+    <t>All of the energy is booked to natural gas, the usual fuel for clay calciners and dryers. Grinding electricity (about 30-45 kWh per metric ton of SCM) is left out, because the clinker it displaces saves a similar amount.</t>
+  </si>
+  <si>
+    <t>SCMEI (BTU per metric ton SCM)</t>
+  </si>
+  <si>
+    <t>The extra SCM is a mix: calcined clay 50%, additional limestone 15%, fly ash 15%, granulated slag 15%, and natural pozzolan 5%. Calcined clay is the remainder once realistic growth in the other materials is counted, because fresh fly ash is shrinking and slag supply is capped. Energy per metric ton: calcined clay 2.3 GJ, harvested fly ash 0.9 GJ for drying (about three quarters of the fly ash; fresh ash needs none), slag 0.3 GJ, natural pozzolan 0.3 GJ, limestone none. The weighted total is 1.31 GJ, or 1,242,825 BTU per metric ton. A reasonable range is 720,000-2,160,000. The mix and the fly ash, slag and pozzolan energy values are our own estimates; no U.S. study gives a marginal SCM mix.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -197,25 +239,24 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -521,115 +562,178 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B35"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" customWidth="1"/>
-    <col min="2" max="2" width="110.7109375" customWidth="1"/>
-    <col min="3" max="3" width="3.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14.6328125" customWidth="1"/>
+    <col min="2" max="2" width="110.6328125" customWidth="1"/>
+    <col min="3" max="3" width="3.6328125" customWidth="1"/>
+    <col min="4" max="4" width="9.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B3" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B4" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B5" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B6" s="6">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B7" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B7" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B8" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B10" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B10" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B11" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B12" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B13" s="6">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B14" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="B15" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B17" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B18" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B19" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B20" s="6">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B21" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B22" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B24" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B25" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B26" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B27" s="6">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="B28" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="B29" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B13" s="6">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B14" s="7" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="B15" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="120" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="75" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>27</v>
+    <row r="33" spans="1:2" ht="116" x14ac:dyDescent="0.35">
+      <c r="A33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="87" x14ac:dyDescent="0.35">
+      <c r="A34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A35" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B7" r:id="rId1" xr:uid="{D986EDBF-0C5E-4687-ABC3-CFF076DAA986}"/>
-    <hyperlink ref="B14" r:id="rId2" xr:uid="{84EBF333-DAA6-4E83-A2B2-4FADF354C64F}"/>
+    <hyperlink ref="B7" r:id="rId1" xr:uid="{EE1980E7-B099-49FF-BA7E-17D0B52EEC6F}"/>
+    <hyperlink ref="B14" r:id="rId2" xr:uid="{E66DD3D7-D521-4DE9-80A7-6DAA5A6D45B6}"/>
+    <hyperlink ref="B21" r:id="rId3" xr:uid="{E794735F-CA37-411C-97AE-6C505BB2F7A5}"/>
+    <hyperlink ref="B28" r:id="rId4" xr:uid="{1CCC15B1-6D64-4B6C-8997-FD30C6680956}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -637,54 +741,112 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="51.36328125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
-        <v>2000000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C4">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B5">
-        <f>1-B3</f>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.15</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="1">
-        <f>B3*B4+B5*B6</f>
-        <v>1000000</v>
+        <v>0.15</v>
+      </c>
+      <c r="C6">
+        <f>0.75*0.9</f>
+        <v>0.67500000000000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7">
+        <v>0.15</v>
+      </c>
+      <c r="C7">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8">
+        <v>0.05</v>
+      </c>
+      <c r="C8">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9">
+        <f>SUM(B4:B8)</f>
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <f>SUMPRODUCT(B4:B8,C4:C8)</f>
+        <v>1.3112499999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11">
+        <v>947817</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12">
+        <f>(C9*B11)</f>
+        <v>1242825.0412499998</v>
       </c>
     </row>
   </sheetData>
@@ -695,20 +857,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="70.7109375" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="1" max="1" width="70.7265625" customWidth="1"/>
+    <col min="2" max="2" width="12.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B3" t="str">
         <f>IF(AND(SCMEI!B2&gt;=0,SCMEI!B2&lt;=3000000),"PASS","FAIL")</f>
@@ -726,23 +888,23 @@
     <tabColor rgb="FF1F3864"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="B1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B2">
-        <f>Derivation!B7</f>
-        <v>1000000</v>
+        <f>Derivation!B12</f>
+        <v>1242825.0412499998</v>
       </c>
     </row>
   </sheetData>
